--- a/data/trans_orig/IP19C02-Provincia-trans_orig.xlsx
+++ b/data/trans_orig/IP19C02-Provincia-trans_orig.xlsx
@@ -733,12 +733,12 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>1209</t>
+          <t>1140</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>6465</t>
+          <t>6119</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -748,12 +748,12 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>6,26%</t>
+          <t>5,9%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>33,46%</t>
+          <t>31,67%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -768,12 +768,12 @@
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>676</t>
+          <t>678</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>5931</t>
+          <t>5610</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -783,12 +783,12 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>2,55%</t>
+          <t>2,56%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>22,36%</t>
+          <t>21,16%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -803,12 +803,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>2523</t>
+          <t>2494</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>9741</t>
+          <t>9749</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -818,12 +818,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>5,5%</t>
+          <t>5,44%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>21,25%</t>
+          <t>21,27%</t>
         </is>
       </c>
     </row>
@@ -846,12 +846,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>12856</t>
+          <t>13202</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>18112</t>
+          <t>18181</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -861,12 +861,12 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>66,54%</t>
+          <t>68,33%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>93,74%</t>
+          <t>94,1%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -881,12 +881,12 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>20587</t>
+          <t>20908</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>25842</t>
+          <t>25840</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -896,12 +896,12 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>77,64%</t>
+          <t>78,84%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>97,45%</t>
+          <t>97,44%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -916,12 +916,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>36098</t>
+          <t>36090</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>43316</t>
+          <t>43345</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -931,12 +931,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>78,75%</t>
+          <t>78,73%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>94,5%</t>
+          <t>94,56%</t>
         </is>
       </c>
     </row>
@@ -1111,12 +1111,12 @@
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>1941</t>
+          <t>1967</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>8591</t>
+          <t>8463</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -1126,12 +1126,12 @@
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>2,99%</t>
+          <t>3,03%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>13,22%</t>
+          <t>13,03%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -1146,12 +1146,12 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>1524</t>
+          <t>1517</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>8936</t>
+          <t>8676</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -1161,12 +1161,12 @@
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>1,25%</t>
+          <t>1,24%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>7,31%</t>
+          <t>7,1%</t>
         </is>
       </c>
     </row>
@@ -1224,12 +1224,12 @@
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>56384</t>
+          <t>56512</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>63034</t>
+          <t>63008</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -1239,12 +1239,12 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>86,78%</t>
+          <t>86,97%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>97,01%</t>
+          <t>96,97%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -1259,12 +1259,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>113261</t>
+          <t>113521</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>120673</t>
+          <t>120680</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -1274,12 +1274,12 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>92,69%</t>
+          <t>92,9%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>98,75%</t>
+          <t>98,76%</t>
         </is>
       </c>
     </row>
@@ -1419,12 +1419,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>684</t>
+          <t>690</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>5889</t>
+          <t>5715</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -1434,12 +1434,12 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>1,99%</t>
+          <t>2,01%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>17,17%</t>
+          <t>16,67%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -1459,7 +1459,7 @@
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>3149</t>
+          <t>3406</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -1474,7 +1474,7 @@
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>8,91%</t>
+          <t>9,64%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -1489,12 +1489,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>794</t>
+          <t>693</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>7849</t>
+          <t>6451</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -1504,12 +1504,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>1,14%</t>
+          <t>1,0%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>11,27%</t>
+          <t>9,27%</t>
         </is>
       </c>
     </row>
@@ -1532,12 +1532,12 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>28403</t>
+          <t>28577</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>33608</t>
+          <t>33602</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -1547,12 +1547,12 @@
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>82,83%</t>
+          <t>83,33%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>98,01%</t>
+          <t>97,99%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -1567,7 +1567,7 @@
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>32180</t>
+          <t>31923</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
@@ -1582,7 +1582,7 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>91,09%</t>
+          <t>90,36%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
@@ -1602,12 +1602,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>61772</t>
+          <t>63170</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>68827</t>
+          <t>68928</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -1617,12 +1617,12 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>88,73%</t>
+          <t>90,73%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>98,86%</t>
+          <t>99,0%</t>
         </is>
       </c>
     </row>
@@ -1767,7 +1767,7 @@
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>4935</t>
+          <t>5417</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -1782,7 +1782,7 @@
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>11,76%</t>
+          <t>12,91%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -1837,7 +1837,7 @@
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>5881</t>
+          <t>5658</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -1852,7 +1852,7 @@
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>7,03%</t>
+          <t>6,77%</t>
         </is>
       </c>
     </row>
@@ -1875,7 +1875,7 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>37024</t>
+          <t>36542</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
@@ -1890,7 +1890,7 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>88,24%</t>
+          <t>87,09%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
@@ -1945,7 +1945,7 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>77719</t>
+          <t>77942</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
@@ -1960,7 +1960,7 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>92,97%</t>
+          <t>93,23%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
@@ -2105,12 +2105,12 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>3296</t>
+          <t>2836</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>10346</t>
+          <t>9656</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -2120,12 +2120,12 @@
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>12,58%</t>
+          <t>10,83%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>39,5%</t>
+          <t>36,87%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -2140,12 +2140,12 @@
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>708</t>
+          <t>727</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>6346</t>
+          <t>6389</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
@@ -2155,12 +2155,12 @@
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>3,15%</t>
+          <t>3,23%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>28,25%</t>
+          <t>28,44%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -2175,12 +2175,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>4909</t>
+          <t>4782</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>14019</t>
+          <t>13607</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -2190,12 +2190,12 @@
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>10,09%</t>
+          <t>9,83%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>28,81%</t>
+          <t>27,96%</t>
         </is>
       </c>
     </row>
@@ -2218,12 +2218,12 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>15845</t>
+          <t>16535</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>22895</t>
+          <t>23355</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -2233,12 +2233,12 @@
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>60,5%</t>
+          <t>63,13%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>87,42%</t>
+          <t>89,17%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -2253,12 +2253,12 @@
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>16121</t>
+          <t>16078</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>21759</t>
+          <t>21740</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
@@ -2268,12 +2268,12 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>71,75%</t>
+          <t>71,56%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>96,85%</t>
+          <t>96,77%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -2288,12 +2288,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>34640</t>
+          <t>35052</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>43750</t>
+          <t>43877</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -2303,12 +2303,12 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>71,19%</t>
+          <t>72,04%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>89,91%</t>
+          <t>90,17%</t>
         </is>
       </c>
     </row>
@@ -2453,7 +2453,7 @@
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>4198</t>
+          <t>4606</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
@@ -2468,7 +2468,7 @@
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>16,57%</t>
+          <t>18,18%</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
@@ -2488,7 +2488,7 @@
       </c>
       <c r="M19" s="2" t="inlineStr">
         <is>
-          <t>4204</t>
+          <t>4034</t>
         </is>
       </c>
       <c r="N19" s="2" t="inlineStr">
@@ -2503,7 +2503,7 @@
       </c>
       <c r="P19" s="2" t="inlineStr">
         <is>
-          <t>14,82%</t>
+          <t>14,23%</t>
         </is>
       </c>
       <c r="Q19" s="2" t="inlineStr">
@@ -2518,12 +2518,12 @@
       </c>
       <c r="S19" s="2" t="inlineStr">
         <is>
-          <t>628</t>
+          <t>632</t>
         </is>
       </c>
       <c r="T19" s="2" t="inlineStr">
         <is>
-          <t>6017</t>
+          <t>5896</t>
         </is>
       </c>
       <c r="U19" s="2" t="inlineStr">
@@ -2533,12 +2533,12 @@
       </c>
       <c r="V19" s="2" t="inlineStr">
         <is>
-          <t>1,17%</t>
+          <t>1,18%</t>
         </is>
       </c>
       <c r="W19" s="2" t="inlineStr">
         <is>
-          <t>11,21%</t>
+          <t>10,98%</t>
         </is>
       </c>
     </row>
@@ -2561,7 +2561,7 @@
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>21142</t>
+          <t>20734</t>
         </is>
       </c>
       <c r="F20" s="2" t="inlineStr">
@@ -2576,7 +2576,7 @@
       </c>
       <c r="H20" s="2" t="inlineStr">
         <is>
-          <t>83,43%</t>
+          <t>81,82%</t>
         </is>
       </c>
       <c r="I20" s="2" t="inlineStr">
@@ -2596,7 +2596,7 @@
       </c>
       <c r="L20" s="2" t="inlineStr">
         <is>
-          <t>24154</t>
+          <t>24324</t>
         </is>
       </c>
       <c r="M20" s="2" t="inlineStr">
@@ -2611,7 +2611,7 @@
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>85,18%</t>
+          <t>85,77%</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
@@ -2631,12 +2631,12 @@
       </c>
       <c r="S20" s="2" t="inlineStr">
         <is>
-          <t>47681</t>
+          <t>47802</t>
         </is>
       </c>
       <c r="T20" s="2" t="inlineStr">
         <is>
-          <t>53070</t>
+          <t>53066</t>
         </is>
       </c>
       <c r="U20" s="2" t="inlineStr">
@@ -2646,12 +2646,12 @@
       </c>
       <c r="V20" s="2" t="inlineStr">
         <is>
-          <t>88,79%</t>
+          <t>89,02%</t>
         </is>
       </c>
       <c r="W20" s="2" t="inlineStr">
         <is>
-          <t>98,83%</t>
+          <t>98,82%</t>
         </is>
       </c>
     </row>
@@ -2791,12 +2791,12 @@
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>2134</t>
+          <t>2101</t>
         </is>
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t>9046</t>
+          <t>9778</t>
         </is>
       </c>
       <c r="G22" s="2" t="inlineStr">
@@ -2806,12 +2806,12 @@
       </c>
       <c r="H22" s="2" t="inlineStr">
         <is>
-          <t>3,27%</t>
+          <t>3,22%</t>
         </is>
       </c>
       <c r="I22" s="2" t="inlineStr">
         <is>
-          <t>13,86%</t>
+          <t>14,98%</t>
         </is>
       </c>
       <c r="J22" s="2" t="inlineStr">
@@ -2826,12 +2826,12 @@
       </c>
       <c r="L22" s="2" t="inlineStr">
         <is>
-          <t>2096</t>
+          <t>2127</t>
         </is>
       </c>
       <c r="M22" s="2" t="inlineStr">
         <is>
-          <t>9864</t>
+          <t>9238</t>
         </is>
       </c>
       <c r="N22" s="2" t="inlineStr">
@@ -2841,12 +2841,12 @@
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>3,08%</t>
+          <t>3,13%</t>
         </is>
       </c>
       <c r="P22" s="2" t="inlineStr">
         <is>
-          <t>14,5%</t>
+          <t>13,58%</t>
         </is>
       </c>
       <c r="Q22" s="2" t="inlineStr">
@@ -2861,12 +2861,12 @@
       </c>
       <c r="S22" s="2" t="inlineStr">
         <is>
-          <t>5571</t>
+          <t>5545</t>
         </is>
       </c>
       <c r="T22" s="2" t="inlineStr">
         <is>
-          <t>16052</t>
+          <t>15888</t>
         </is>
       </c>
       <c r="U22" s="2" t="inlineStr">
@@ -2876,12 +2876,12 @@
       </c>
       <c r="V22" s="2" t="inlineStr">
         <is>
-          <t>4,18%</t>
+          <t>4,16%</t>
         </is>
       </c>
       <c r="W22" s="2" t="inlineStr">
         <is>
-          <t>12,04%</t>
+          <t>11,92%</t>
         </is>
       </c>
     </row>
@@ -2904,12 +2904,12 @@
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t>56238</t>
+          <t>55506</t>
         </is>
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
-          <t>63150</t>
+          <t>63183</t>
         </is>
       </c>
       <c r="G23" s="2" t="inlineStr">
@@ -2919,12 +2919,12 @@
       </c>
       <c r="H23" s="2" t="inlineStr">
         <is>
-          <t>86,14%</t>
+          <t>85,02%</t>
         </is>
       </c>
       <c r="I23" s="2" t="inlineStr">
         <is>
-          <t>96,73%</t>
+          <t>96,78%</t>
         </is>
       </c>
       <c r="J23" s="2" t="inlineStr">
@@ -2939,12 +2939,12 @@
       </c>
       <c r="L23" s="2" t="inlineStr">
         <is>
-          <t>58165</t>
+          <t>58791</t>
         </is>
       </c>
       <c r="M23" s="2" t="inlineStr">
         <is>
-          <t>65933</t>
+          <t>65902</t>
         </is>
       </c>
       <c r="N23" s="2" t="inlineStr">
@@ -2954,12 +2954,12 @@
       </c>
       <c r="O23" s="2" t="inlineStr">
         <is>
-          <t>85,5%</t>
+          <t>86,42%</t>
         </is>
       </c>
       <c r="P23" s="2" t="inlineStr">
         <is>
-          <t>96,92%</t>
+          <t>96,87%</t>
         </is>
       </c>
       <c r="Q23" s="2" t="inlineStr">
@@ -2974,12 +2974,12 @@
       </c>
       <c r="S23" s="2" t="inlineStr">
         <is>
-          <t>117262</t>
+          <t>117426</t>
         </is>
       </c>
       <c r="T23" s="2" t="inlineStr">
         <is>
-          <t>127743</t>
+          <t>127769</t>
         </is>
       </c>
       <c r="U23" s="2" t="inlineStr">
@@ -2989,12 +2989,12 @@
       </c>
       <c r="V23" s="2" t="inlineStr">
         <is>
-          <t>87,96%</t>
+          <t>88,08%</t>
         </is>
       </c>
       <c r="W23" s="2" t="inlineStr">
         <is>
-          <t>95,82%</t>
+          <t>95,84%</t>
         </is>
       </c>
     </row>
@@ -3134,12 +3134,12 @@
       </c>
       <c r="E25" s="2" t="inlineStr">
         <is>
-          <t>3441</t>
+          <t>3286</t>
         </is>
       </c>
       <c r="F25" s="2" t="inlineStr">
         <is>
-          <t>10959</t>
+          <t>10630</t>
         </is>
       </c>
       <c r="G25" s="2" t="inlineStr">
@@ -3149,12 +3149,12 @@
       </c>
       <c r="H25" s="2" t="inlineStr">
         <is>
-          <t>4,23%</t>
+          <t>4,04%</t>
         </is>
       </c>
       <c r="I25" s="2" t="inlineStr">
         <is>
-          <t>13,48%</t>
+          <t>13,07%</t>
         </is>
       </c>
       <c r="J25" s="2" t="inlineStr">
@@ -3169,12 +3169,12 @@
       </c>
       <c r="L25" s="2" t="inlineStr">
         <is>
-          <t>4496</t>
+          <t>4696</t>
         </is>
       </c>
       <c r="M25" s="2" t="inlineStr">
         <is>
-          <t>13052</t>
+          <t>13665</t>
         </is>
       </c>
       <c r="N25" s="2" t="inlineStr">
@@ -3184,12 +3184,12 @@
       </c>
       <c r="O25" s="2" t="inlineStr">
         <is>
-          <t>6,04%</t>
+          <t>6,31%</t>
         </is>
       </c>
       <c r="P25" s="2" t="inlineStr">
         <is>
-          <t>17,54%</t>
+          <t>18,36%</t>
         </is>
       </c>
       <c r="Q25" s="2" t="inlineStr">
@@ -3204,12 +3204,12 @@
       </c>
       <c r="S25" s="2" t="inlineStr">
         <is>
-          <t>9959</t>
+          <t>9611</t>
         </is>
       </c>
       <c r="T25" s="2" t="inlineStr">
         <is>
-          <t>21060</t>
+          <t>21551</t>
         </is>
       </c>
       <c r="U25" s="2" t="inlineStr">
@@ -3219,12 +3219,12 @@
       </c>
       <c r="V25" s="2" t="inlineStr">
         <is>
-          <t>6,39%</t>
+          <t>6,17%</t>
         </is>
       </c>
       <c r="W25" s="2" t="inlineStr">
         <is>
-          <t>13,52%</t>
+          <t>13,84%</t>
         </is>
       </c>
     </row>
@@ -3247,12 +3247,12 @@
       </c>
       <c r="E26" s="2" t="inlineStr">
         <is>
-          <t>70361</t>
+          <t>70690</t>
         </is>
       </c>
       <c r="F26" s="2" t="inlineStr">
         <is>
-          <t>77879</t>
+          <t>78034</t>
         </is>
       </c>
       <c r="G26" s="2" t="inlineStr">
@@ -3262,12 +3262,12 @@
       </c>
       <c r="H26" s="2" t="inlineStr">
         <is>
-          <t>86,52%</t>
+          <t>86,93%</t>
         </is>
       </c>
       <c r="I26" s="2" t="inlineStr">
         <is>
-          <t>95,77%</t>
+          <t>95,96%</t>
         </is>
       </c>
       <c r="J26" s="2" t="inlineStr">
@@ -3282,12 +3282,12 @@
       </c>
       <c r="L26" s="2" t="inlineStr">
         <is>
-          <t>61361</t>
+          <t>60748</t>
         </is>
       </c>
       <c r="M26" s="2" t="inlineStr">
         <is>
-          <t>69917</t>
+          <t>69717</t>
         </is>
       </c>
       <c r="N26" s="2" t="inlineStr">
@@ -3297,12 +3297,12 @@
       </c>
       <c r="O26" s="2" t="inlineStr">
         <is>
-          <t>82,46%</t>
+          <t>81,64%</t>
         </is>
       </c>
       <c r="P26" s="2" t="inlineStr">
         <is>
-          <t>93,96%</t>
+          <t>93,69%</t>
         </is>
       </c>
       <c r="Q26" s="2" t="inlineStr">
@@ -3317,12 +3317,12 @@
       </c>
       <c r="S26" s="2" t="inlineStr">
         <is>
-          <t>134674</t>
+          <t>134183</t>
         </is>
       </c>
       <c r="T26" s="2" t="inlineStr">
         <is>
-          <t>145775</t>
+          <t>146123</t>
         </is>
       </c>
       <c r="U26" s="2" t="inlineStr">
@@ -3332,12 +3332,12 @@
       </c>
       <c r="V26" s="2" t="inlineStr">
         <is>
-          <t>86,48%</t>
+          <t>86,16%</t>
         </is>
       </c>
       <c r="W26" s="2" t="inlineStr">
         <is>
-          <t>93,61%</t>
+          <t>93,83%</t>
         </is>
       </c>
     </row>
@@ -3477,12 +3477,12 @@
       </c>
       <c r="E28" s="2" t="inlineStr">
         <is>
-          <t>18261</t>
+          <t>18506</t>
         </is>
       </c>
       <c r="F28" s="2" t="inlineStr">
         <is>
-          <t>33783</t>
+          <t>34662</t>
         </is>
       </c>
       <c r="G28" s="2" t="inlineStr">
@@ -3492,12 +3492,12 @@
       </c>
       <c r="H28" s="2" t="inlineStr">
         <is>
-          <t>5,2%</t>
+          <t>5,27%</t>
         </is>
       </c>
       <c r="I28" s="2" t="inlineStr">
         <is>
-          <t>9,63%</t>
+          <t>9,88%</t>
         </is>
       </c>
       <c r="J28" s="2" t="inlineStr">
@@ -3512,12 +3512,12 @@
       </c>
       <c r="L28" s="2" t="inlineStr">
         <is>
-          <t>17678</t>
+          <t>17312</t>
         </is>
       </c>
       <c r="M28" s="2" t="inlineStr">
         <is>
-          <t>32695</t>
+          <t>32665</t>
         </is>
       </c>
       <c r="N28" s="2" t="inlineStr">
@@ -3527,12 +3527,12 @@
       </c>
       <c r="O28" s="2" t="inlineStr">
         <is>
-          <t>4,89%</t>
+          <t>4,79%</t>
         </is>
       </c>
       <c r="P28" s="2" t="inlineStr">
         <is>
-          <t>9,04%</t>
+          <t>9,03%</t>
         </is>
       </c>
       <c r="Q28" s="2" t="inlineStr">
@@ -3547,12 +3547,12 @@
       </c>
       <c r="S28" s="2" t="inlineStr">
         <is>
-          <t>39392</t>
+          <t>39819</t>
         </is>
       </c>
       <c r="T28" s="2" t="inlineStr">
         <is>
-          <t>61615</t>
+          <t>60805</t>
         </is>
       </c>
       <c r="U28" s="2" t="inlineStr">
@@ -3562,12 +3562,12 @@
       </c>
       <c r="V28" s="2" t="inlineStr">
         <is>
-          <t>5,53%</t>
+          <t>5,59%</t>
         </is>
       </c>
       <c r="W28" s="2" t="inlineStr">
         <is>
-          <t>8,65%</t>
+          <t>8,53%</t>
         </is>
       </c>
     </row>
@@ -3590,12 +3590,12 @@
       </c>
       <c r="E29" s="2" t="inlineStr">
         <is>
-          <t>317147</t>
+          <t>316268</t>
         </is>
       </c>
       <c r="F29" s="2" t="inlineStr">
         <is>
-          <t>332669</t>
+          <t>332424</t>
         </is>
       </c>
       <c r="G29" s="2" t="inlineStr">
@@ -3605,12 +3605,12 @@
       </c>
       <c r="H29" s="2" t="inlineStr">
         <is>
-          <t>90,37%</t>
+          <t>90,12%</t>
         </is>
       </c>
       <c r="I29" s="2" t="inlineStr">
         <is>
-          <t>94,8%</t>
+          <t>94,73%</t>
         </is>
       </c>
       <c r="J29" s="2" t="inlineStr">
@@ -3625,12 +3625,12 @@
       </c>
       <c r="L29" s="2" t="inlineStr">
         <is>
-          <t>329036</t>
+          <t>329066</t>
         </is>
       </c>
       <c r="M29" s="2" t="inlineStr">
         <is>
-          <t>344053</t>
+          <t>344419</t>
         </is>
       </c>
       <c r="N29" s="2" t="inlineStr">
@@ -3640,12 +3640,12 @@
       </c>
       <c r="O29" s="2" t="inlineStr">
         <is>
-          <t>90,96%</t>
+          <t>90,97%</t>
         </is>
       </c>
       <c r="P29" s="2" t="inlineStr">
         <is>
-          <t>95,11%</t>
+          <t>95,21%</t>
         </is>
       </c>
       <c r="Q29" s="2" t="inlineStr">
@@ -3660,12 +3660,12 @@
       </c>
       <c r="S29" s="2" t="inlineStr">
         <is>
-          <t>651046</t>
+          <t>651856</t>
         </is>
       </c>
       <c r="T29" s="2" t="inlineStr">
         <is>
-          <t>673269</t>
+          <t>672842</t>
         </is>
       </c>
       <c r="U29" s="2" t="inlineStr">
@@ -3675,12 +3675,12 @@
       </c>
       <c r="V29" s="2" t="inlineStr">
         <is>
-          <t>91,35%</t>
+          <t>91,47%</t>
         </is>
       </c>
       <c r="W29" s="2" t="inlineStr">
         <is>
-          <t>94,47%</t>
+          <t>94,41%</t>
         </is>
       </c>
     </row>
@@ -4061,7 +4061,7 @@
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>4100</t>
+          <t>4421</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -4076,7 +4076,7 @@
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>18,32%</t>
+          <t>19,76%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -4091,12 +4091,12 @@
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>585</t>
+          <t>606</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>5143</t>
+          <t>5182</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -4106,12 +4106,12 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>1,97%</t>
+          <t>2,04%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>17,34%</t>
+          <t>17,47%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -4126,12 +4126,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>663</t>
+          <t>1190</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>6253</t>
+          <t>6736</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -4141,12 +4141,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>1,27%</t>
+          <t>2,29%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>12,02%</t>
+          <t>12,95%</t>
         </is>
       </c>
     </row>
@@ -4169,7 +4169,7 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>18275</t>
+          <t>17954</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
@@ -4184,7 +4184,7 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>81,68%</t>
+          <t>80,24%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
@@ -4204,12 +4204,12 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>24516</t>
+          <t>24477</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>29074</t>
+          <t>29053</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -4219,12 +4219,12 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>82,66%</t>
+          <t>82,53%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>98,03%</t>
+          <t>97,96%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -4239,12 +4239,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>45781</t>
+          <t>45298</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>51371</t>
+          <t>50844</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -4254,12 +4254,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>87,98%</t>
+          <t>87,05%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>98,73%</t>
+          <t>97,71%</t>
         </is>
       </c>
     </row>
@@ -4399,12 +4399,12 @@
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>622</t>
+          <t>0</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>5339</t>
+          <t>4832</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -4414,12 +4414,12 @@
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>1,17%</t>
+          <t>0,0%</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>10,07%</t>
+          <t>9,11%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -4434,12 +4434,12 @@
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>596</t>
+          <t>598</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>5826</t>
+          <t>5941</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -4449,12 +4449,12 @@
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>1,03%</t>
+          <t>1,04%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>10,11%</t>
+          <t>10,31%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -4469,12 +4469,12 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>1849</t>
+          <t>1894</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>8206</t>
+          <t>9108</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -4484,12 +4484,12 @@
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>1,67%</t>
+          <t>1,71%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>7,41%</t>
+          <t>8,23%</t>
         </is>
       </c>
     </row>
@@ -4512,12 +4512,12 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>47705</t>
+          <t>48212</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>52422</t>
+          <t>53044</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -4527,12 +4527,12 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>89,93%</t>
+          <t>90,89%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>98,83%</t>
+          <t>100,0%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -4547,12 +4547,12 @@
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>51806</t>
+          <t>51691</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>57036</t>
+          <t>57034</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -4562,12 +4562,12 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>89,89%</t>
+          <t>89,69%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>98,97%</t>
+          <t>98,96%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -4582,12 +4582,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>102471</t>
+          <t>101569</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>108828</t>
+          <t>108783</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -4597,12 +4597,12 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>92,59%</t>
+          <t>91,77%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>98,33%</t>
+          <t>98,29%</t>
         </is>
       </c>
     </row>
@@ -4747,7 +4747,7 @@
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>3631</t>
+          <t>3326</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -4762,7 +4762,7 @@
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>10,85%</t>
+          <t>9,94%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -4777,12 +4777,12 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>682</t>
+          <t>681</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>5618</t>
+          <t>5728</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -4797,7 +4797,7 @@
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>14,24%</t>
+          <t>14,52%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -4812,12 +4812,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>705</t>
+          <t>735</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>6394</t>
+          <t>6918</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -4827,12 +4827,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>0,97%</t>
+          <t>1,01%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>8,77%</t>
+          <t>9,49%</t>
         </is>
       </c>
     </row>
@@ -4855,7 +4855,7 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>29832</t>
+          <t>30137</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
@@ -4870,7 +4870,7 @@
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>89,15%</t>
+          <t>90,06%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
@@ -4890,12 +4890,12 @@
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>33827</t>
+          <t>33717</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>38763</t>
+          <t>38764</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
@@ -4905,7 +4905,7 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>85,76%</t>
+          <t>85,48%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
@@ -4925,12 +4925,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>66514</t>
+          <t>65990</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>72203</t>
+          <t>72173</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -4940,12 +4940,12 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>91,23%</t>
+          <t>90,51%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>99,03%</t>
+          <t>98,99%</t>
         </is>
       </c>
     </row>
@@ -5090,7 +5090,7 @@
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>3768</t>
+          <t>3520</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -5105,7 +5105,7 @@
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>9,02%</t>
+          <t>8,42%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -5120,12 +5120,12 @@
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>1307</t>
+          <t>1290</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>8335</t>
+          <t>8775</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -5135,12 +5135,12 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>3,17%</t>
+          <t>3,13%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>20,22%</t>
+          <t>21,28%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -5155,12 +5155,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>1953</t>
+          <t>1965</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>10739</t>
+          <t>10284</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -5170,12 +5170,12 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>2,35%</t>
+          <t>2,37%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>12,93%</t>
+          <t>12,39%</t>
         </is>
       </c>
     </row>
@@ -5198,7 +5198,7 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>38030</t>
+          <t>38278</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
@@ -5213,7 +5213,7 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>90,98%</t>
+          <t>91,58%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
@@ -5233,12 +5233,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>32891</t>
+          <t>32451</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>39919</t>
+          <t>39936</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -5248,12 +5248,12 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>79,78%</t>
+          <t>78,72%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>96,83%</t>
+          <t>96,87%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -5268,12 +5268,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>72285</t>
+          <t>72740</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>81071</t>
+          <t>81059</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -5283,12 +5283,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>87,07%</t>
+          <t>87,61%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>97,65%</t>
+          <t>97,63%</t>
         </is>
       </c>
     </row>
@@ -5433,7 +5433,7 @@
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>5049</t>
+          <t>5097</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -5448,7 +5448,7 @@
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>19,37%</t>
+          <t>19,55%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -5468,7 +5468,7 @@
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>4016</t>
+          <t>4576</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
@@ -5483,7 +5483,7 @@
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>14,54%</t>
+          <t>16,56%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -5498,12 +5498,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>752</t>
+          <t>760</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>7530</t>
+          <t>6885</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -5513,12 +5513,12 @@
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>1,4%</t>
+          <t>1,41%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>14,02%</t>
+          <t>12,82%</t>
         </is>
       </c>
     </row>
@@ -5541,7 +5541,7 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>21019</t>
+          <t>20971</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
@@ -5556,7 +5556,7 @@
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>80,63%</t>
+          <t>80,45%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
@@ -5576,7 +5576,7 @@
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>23614</t>
+          <t>23054</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
@@ -5591,7 +5591,7 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>85,46%</t>
+          <t>83,44%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
@@ -5611,12 +5611,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>46168</t>
+          <t>46813</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>52946</t>
+          <t>52938</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -5626,12 +5626,12 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>85,98%</t>
+          <t>87,18%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>98,6%</t>
+          <t>98,59%</t>
         </is>
       </c>
     </row>
@@ -5771,12 +5771,12 @@
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>709</t>
+          <t>696</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>5904</t>
+          <t>5441</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
@@ -5786,12 +5786,12 @@
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>2,04%</t>
+          <t>2,01%</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>17,02%</t>
+          <t>15,69%</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
@@ -5806,12 +5806,12 @@
       </c>
       <c r="L19" s="2" t="inlineStr">
         <is>
-          <t>691</t>
+          <t>699</t>
         </is>
       </c>
       <c r="M19" s="2" t="inlineStr">
         <is>
-          <t>6697</t>
+          <t>6414</t>
         </is>
       </c>
       <c r="N19" s="2" t="inlineStr">
@@ -5821,12 +5821,12 @@
       </c>
       <c r="O19" s="2" t="inlineStr">
         <is>
-          <t>2,08%</t>
+          <t>2,11%</t>
         </is>
       </c>
       <c r="P19" s="2" t="inlineStr">
         <is>
-          <t>20,2%</t>
+          <t>19,34%</t>
         </is>
       </c>
       <c r="Q19" s="2" t="inlineStr">
@@ -5841,12 +5841,12 @@
       </c>
       <c r="S19" s="2" t="inlineStr">
         <is>
-          <t>2182</t>
+          <t>2184</t>
         </is>
       </c>
       <c r="T19" s="2" t="inlineStr">
         <is>
-          <t>10190</t>
+          <t>9642</t>
         </is>
       </c>
       <c r="U19" s="2" t="inlineStr">
@@ -5861,7 +5861,7 @@
       </c>
       <c r="W19" s="2" t="inlineStr">
         <is>
-          <t>15,02%</t>
+          <t>14,21%</t>
         </is>
       </c>
     </row>
@@ -5884,12 +5884,12 @@
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>28776</t>
+          <t>29239</t>
         </is>
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>33971</t>
+          <t>33984</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
@@ -5899,12 +5899,12 @@
       </c>
       <c r="H20" s="2" t="inlineStr">
         <is>
-          <t>82,98%</t>
+          <t>84,31%</t>
         </is>
       </c>
       <c r="I20" s="2" t="inlineStr">
         <is>
-          <t>97,96%</t>
+          <t>97,99%</t>
         </is>
       </c>
       <c r="J20" s="2" t="inlineStr">
@@ -5919,12 +5919,12 @@
       </c>
       <c r="L20" s="2" t="inlineStr">
         <is>
-          <t>26462</t>
+          <t>26745</t>
         </is>
       </c>
       <c r="M20" s="2" t="inlineStr">
         <is>
-          <t>32468</t>
+          <t>32460</t>
         </is>
       </c>
       <c r="N20" s="2" t="inlineStr">
@@ -5934,12 +5934,12 @@
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>79,8%</t>
+          <t>80,66%</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
         <is>
-          <t>97,92%</t>
+          <t>97,89%</t>
         </is>
       </c>
       <c r="Q20" s="2" t="inlineStr">
@@ -5954,12 +5954,12 @@
       </c>
       <c r="S20" s="2" t="inlineStr">
         <is>
-          <t>57648</t>
+          <t>58196</t>
         </is>
       </c>
       <c r="T20" s="2" t="inlineStr">
         <is>
-          <t>65656</t>
+          <t>65654</t>
         </is>
       </c>
       <c r="U20" s="2" t="inlineStr">
@@ -5969,7 +5969,7 @@
       </c>
       <c r="V20" s="2" t="inlineStr">
         <is>
-          <t>84,98%</t>
+          <t>85,79%</t>
         </is>
       </c>
       <c r="W20" s="2" t="inlineStr">
@@ -6114,12 +6114,12 @@
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>738</t>
+          <t>733</t>
         </is>
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t>7319</t>
+          <t>8257</t>
         </is>
       </c>
       <c r="G22" s="2" t="inlineStr">
@@ -6134,7 +6134,7 @@
       </c>
       <c r="I22" s="2" t="inlineStr">
         <is>
-          <t>11,44%</t>
+          <t>12,91%</t>
         </is>
       </c>
       <c r="J22" s="2" t="inlineStr">
@@ -6149,12 +6149,12 @@
       </c>
       <c r="L22" s="2" t="inlineStr">
         <is>
-          <t>653</t>
+          <t>638</t>
         </is>
       </c>
       <c r="M22" s="2" t="inlineStr">
         <is>
-          <t>6066</t>
+          <t>6384</t>
         </is>
       </c>
       <c r="N22" s="2" t="inlineStr">
@@ -6164,12 +6164,12 @@
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>0,97%</t>
+          <t>0,95%</t>
         </is>
       </c>
       <c r="P22" s="2" t="inlineStr">
         <is>
-          <t>9,03%</t>
+          <t>9,5%</t>
         </is>
       </c>
       <c r="Q22" s="2" t="inlineStr">
@@ -6184,12 +6184,12 @@
       </c>
       <c r="S22" s="2" t="inlineStr">
         <is>
-          <t>2692</t>
+          <t>2561</t>
         </is>
       </c>
       <c r="T22" s="2" t="inlineStr">
         <is>
-          <t>10255</t>
+          <t>10314</t>
         </is>
       </c>
       <c r="U22" s="2" t="inlineStr">
@@ -6199,12 +6199,12 @@
       </c>
       <c r="V22" s="2" t="inlineStr">
         <is>
-          <t>2,05%</t>
+          <t>1,95%</t>
         </is>
       </c>
       <c r="W22" s="2" t="inlineStr">
         <is>
-          <t>7,82%</t>
+          <t>7,87%</t>
         </is>
       </c>
     </row>
@@ -6227,12 +6227,12 @@
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t>56650</t>
+          <t>55712</t>
         </is>
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
-          <t>63231</t>
+          <t>63236</t>
         </is>
       </c>
       <c r="G23" s="2" t="inlineStr">
@@ -6242,7 +6242,7 @@
       </c>
       <c r="H23" s="2" t="inlineStr">
         <is>
-          <t>88,56%</t>
+          <t>87,09%</t>
         </is>
       </c>
       <c r="I23" s="2" t="inlineStr">
@@ -6262,12 +6262,12 @@
       </c>
       <c r="L23" s="2" t="inlineStr">
         <is>
-          <t>61098</t>
+          <t>60780</t>
         </is>
       </c>
       <c r="M23" s="2" t="inlineStr">
         <is>
-          <t>66511</t>
+          <t>66526</t>
         </is>
       </c>
       <c r="N23" s="2" t="inlineStr">
@@ -6277,12 +6277,12 @@
       </c>
       <c r="O23" s="2" t="inlineStr">
         <is>
-          <t>90,97%</t>
+          <t>90,5%</t>
         </is>
       </c>
       <c r="P23" s="2" t="inlineStr">
         <is>
-          <t>99,03%</t>
+          <t>99,05%</t>
         </is>
       </c>
       <c r="Q23" s="2" t="inlineStr">
@@ -6297,12 +6297,12 @@
       </c>
       <c r="S23" s="2" t="inlineStr">
         <is>
-          <t>120878</t>
+          <t>120819</t>
         </is>
       </c>
       <c r="T23" s="2" t="inlineStr">
         <is>
-          <t>128441</t>
+          <t>128572</t>
         </is>
       </c>
       <c r="U23" s="2" t="inlineStr">
@@ -6312,12 +6312,12 @@
       </c>
       <c r="V23" s="2" t="inlineStr">
         <is>
-          <t>92,18%</t>
+          <t>92,13%</t>
         </is>
       </c>
       <c r="W23" s="2" t="inlineStr">
         <is>
-          <t>97,95%</t>
+          <t>98,05%</t>
         </is>
       </c>
     </row>
@@ -6457,12 +6457,12 @@
       </c>
       <c r="E25" s="2" t="inlineStr">
         <is>
-          <t>4964</t>
+          <t>5053</t>
         </is>
       </c>
       <c r="F25" s="2" t="inlineStr">
         <is>
-          <t>14198</t>
+          <t>14167</t>
         </is>
       </c>
       <c r="G25" s="2" t="inlineStr">
@@ -6472,12 +6472,12 @@
       </c>
       <c r="H25" s="2" t="inlineStr">
         <is>
-          <t>6,38%</t>
+          <t>6,49%</t>
         </is>
       </c>
       <c r="I25" s="2" t="inlineStr">
         <is>
-          <t>18,24%</t>
+          <t>18,2%</t>
         </is>
       </c>
       <c r="J25" s="2" t="inlineStr">
@@ -6492,12 +6492,12 @@
       </c>
       <c r="L25" s="2" t="inlineStr">
         <is>
-          <t>3258</t>
+          <t>3032</t>
         </is>
       </c>
       <c r="M25" s="2" t="inlineStr">
         <is>
-          <t>11364</t>
+          <t>11369</t>
         </is>
       </c>
       <c r="N25" s="2" t="inlineStr">
@@ -6507,12 +6507,12 @@
       </c>
       <c r="O25" s="2" t="inlineStr">
         <is>
-          <t>4,65%</t>
+          <t>4,33%</t>
         </is>
       </c>
       <c r="P25" s="2" t="inlineStr">
         <is>
-          <t>16,21%</t>
+          <t>16,22%</t>
         </is>
       </c>
       <c r="Q25" s="2" t="inlineStr">
@@ -6527,12 +6527,12 @@
       </c>
       <c r="S25" s="2" t="inlineStr">
         <is>
-          <t>9877</t>
+          <t>9748</t>
         </is>
       </c>
       <c r="T25" s="2" t="inlineStr">
         <is>
-          <t>21643</t>
+          <t>22052</t>
         </is>
       </c>
       <c r="U25" s="2" t="inlineStr">
@@ -6542,12 +6542,12 @@
       </c>
       <c r="V25" s="2" t="inlineStr">
         <is>
-          <t>6,68%</t>
+          <t>6,59%</t>
         </is>
       </c>
       <c r="W25" s="2" t="inlineStr">
         <is>
-          <t>14,63%</t>
+          <t>14,91%</t>
         </is>
       </c>
     </row>
@@ -6570,12 +6570,12 @@
       </c>
       <c r="E26" s="2" t="inlineStr">
         <is>
-          <t>63649</t>
+          <t>63680</t>
         </is>
       </c>
       <c r="F26" s="2" t="inlineStr">
         <is>
-          <t>72883</t>
+          <t>72794</t>
         </is>
       </c>
       <c r="G26" s="2" t="inlineStr">
@@ -6585,12 +6585,12 @@
       </c>
       <c r="H26" s="2" t="inlineStr">
         <is>
-          <t>81,76%</t>
+          <t>81,8%</t>
         </is>
       </c>
       <c r="I26" s="2" t="inlineStr">
         <is>
-          <t>93,62%</t>
+          <t>93,51%</t>
         </is>
       </c>
       <c r="J26" s="2" t="inlineStr">
@@ -6605,12 +6605,12 @@
       </c>
       <c r="L26" s="2" t="inlineStr">
         <is>
-          <t>58723</t>
+          <t>58718</t>
         </is>
       </c>
       <c r="M26" s="2" t="inlineStr">
         <is>
-          <t>66829</t>
+          <t>67055</t>
         </is>
       </c>
       <c r="N26" s="2" t="inlineStr">
@@ -6620,12 +6620,12 @@
       </c>
       <c r="O26" s="2" t="inlineStr">
         <is>
-          <t>83,79%</t>
+          <t>83,78%</t>
         </is>
       </c>
       <c r="P26" s="2" t="inlineStr">
         <is>
-          <t>95,35%</t>
+          <t>95,67%</t>
         </is>
       </c>
       <c r="Q26" s="2" t="inlineStr">
@@ -6640,12 +6640,12 @@
       </c>
       <c r="S26" s="2" t="inlineStr">
         <is>
-          <t>126291</t>
+          <t>125882</t>
         </is>
       </c>
       <c r="T26" s="2" t="inlineStr">
         <is>
-          <t>138057</t>
+          <t>138186</t>
         </is>
       </c>
       <c r="U26" s="2" t="inlineStr">
@@ -6655,12 +6655,12 @@
       </c>
       <c r="V26" s="2" t="inlineStr">
         <is>
-          <t>85,37%</t>
+          <t>85,09%</t>
         </is>
       </c>
       <c r="W26" s="2" t="inlineStr">
         <is>
-          <t>93,32%</t>
+          <t>93,41%</t>
         </is>
       </c>
     </row>
@@ -6800,12 +6800,12 @@
       </c>
       <c r="E28" s="2" t="inlineStr">
         <is>
-          <t>13779</t>
+          <t>13830</t>
         </is>
       </c>
       <c r="F28" s="2" t="inlineStr">
         <is>
-          <t>28946</t>
+          <t>27968</t>
         </is>
       </c>
       <c r="G28" s="2" t="inlineStr">
@@ -6815,12 +6815,12 @@
       </c>
       <c r="H28" s="2" t="inlineStr">
         <is>
-          <t>3,9%</t>
+          <t>3,92%</t>
         </is>
       </c>
       <c r="I28" s="2" t="inlineStr">
         <is>
-          <t>8,19%</t>
+          <t>7,92%</t>
         </is>
       </c>
       <c r="J28" s="2" t="inlineStr">
@@ -6835,12 +6835,12 @@
       </c>
       <c r="L28" s="2" t="inlineStr">
         <is>
-          <t>16876</t>
+          <t>16690</t>
         </is>
       </c>
       <c r="M28" s="2" t="inlineStr">
         <is>
-          <t>32379</t>
+          <t>31697</t>
         </is>
       </c>
       <c r="N28" s="2" t="inlineStr">
@@ -6850,12 +6850,12 @@
       </c>
       <c r="O28" s="2" t="inlineStr">
         <is>
-          <t>4,61%</t>
+          <t>4,56%</t>
         </is>
       </c>
       <c r="P28" s="2" t="inlineStr">
         <is>
-          <t>8,85%</t>
+          <t>8,66%</t>
         </is>
       </c>
       <c r="Q28" s="2" t="inlineStr">
@@ -6870,12 +6870,12 @@
       </c>
       <c r="S28" s="2" t="inlineStr">
         <is>
-          <t>34252</t>
+          <t>34508</t>
         </is>
       </c>
       <c r="T28" s="2" t="inlineStr">
         <is>
-          <t>56189</t>
+          <t>53864</t>
         </is>
       </c>
       <c r="U28" s="2" t="inlineStr">
@@ -6885,12 +6885,12 @@
       </c>
       <c r="V28" s="2" t="inlineStr">
         <is>
-          <t>4,76%</t>
+          <t>4,8%</t>
         </is>
       </c>
       <c r="W28" s="2" t="inlineStr">
         <is>
-          <t>7,81%</t>
+          <t>7,49%</t>
         </is>
       </c>
     </row>
@@ -6913,12 +6913,12 @@
       </c>
       <c r="E29" s="2" t="inlineStr">
         <is>
-          <t>324298</t>
+          <t>325276</t>
         </is>
       </c>
       <c r="F29" s="2" t="inlineStr">
         <is>
-          <t>339465</t>
+          <t>339414</t>
         </is>
       </c>
       <c r="G29" s="2" t="inlineStr">
@@ -6928,12 +6928,12 @@
       </c>
       <c r="H29" s="2" t="inlineStr">
         <is>
-          <t>91,81%</t>
+          <t>92,08%</t>
         </is>
       </c>
       <c r="I29" s="2" t="inlineStr">
         <is>
-          <t>96,1%</t>
+          <t>96,08%</t>
         </is>
       </c>
       <c r="J29" s="2" t="inlineStr">
@@ -6948,12 +6948,12 @@
       </c>
       <c r="L29" s="2" t="inlineStr">
         <is>
-          <t>333623</t>
+          <t>334305</t>
         </is>
       </c>
       <c r="M29" s="2" t="inlineStr">
         <is>
-          <t>349126</t>
+          <t>349312</t>
         </is>
       </c>
       <c r="N29" s="2" t="inlineStr">
@@ -6963,12 +6963,12 @@
       </c>
       <c r="O29" s="2" t="inlineStr">
         <is>
-          <t>91,15%</t>
+          <t>91,34%</t>
         </is>
       </c>
       <c r="P29" s="2" t="inlineStr">
         <is>
-          <t>95,39%</t>
+          <t>95,44%</t>
         </is>
       </c>
       <c r="Q29" s="2" t="inlineStr">
@@ -6983,12 +6983,12 @@
       </c>
       <c r="S29" s="2" t="inlineStr">
         <is>
-          <t>663057</t>
+          <t>665382</t>
         </is>
       </c>
       <c r="T29" s="2" t="inlineStr">
         <is>
-          <t>684994</t>
+          <t>684738</t>
         </is>
       </c>
       <c r="U29" s="2" t="inlineStr">
@@ -6998,12 +6998,12 @@
       </c>
       <c r="V29" s="2" t="inlineStr">
         <is>
-          <t>92,19%</t>
+          <t>92,51%</t>
         </is>
       </c>
       <c r="W29" s="2" t="inlineStr">
         <is>
-          <t>95,24%</t>
+          <t>95,2%</t>
         </is>
       </c>
     </row>
@@ -7379,12 +7379,12 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>545</t>
+          <t>574</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>5236</t>
+          <t>4932</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -7394,12 +7394,12 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>1,91%</t>
+          <t>2,01%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>18,33%</t>
+          <t>17,27%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -7419,7 +7419,7 @@
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>3262</t>
+          <t>3249</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -7434,7 +7434,7 @@
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>10,91%</t>
+          <t>10,86%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -7449,12 +7449,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>1091</t>
+          <t>1072</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>6122</t>
+          <t>6195</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -7464,12 +7464,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>1,87%</t>
+          <t>1,83%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>10,47%</t>
+          <t>10,59%</t>
         </is>
       </c>
     </row>
@@ -7492,12 +7492,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>23330</t>
+          <t>23634</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>28021</t>
+          <t>27992</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -7507,12 +7507,12 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>81,67%</t>
+          <t>82,73%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>98,09%</t>
+          <t>97,99%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -7527,7 +7527,7 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>26649</t>
+          <t>26662</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
@@ -7542,7 +7542,7 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>89,09%</t>
+          <t>89,14%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
@@ -7562,12 +7562,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>52354</t>
+          <t>52281</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>57385</t>
+          <t>57404</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -7577,12 +7577,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>89,53%</t>
+          <t>89,41%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>98,13%</t>
+          <t>98,17%</t>
         </is>
       </c>
     </row>
@@ -7727,7 +7727,7 @@
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>4007</t>
+          <t>4089</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -7742,7 +7742,7 @@
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>7,49%</t>
+          <t>7,64%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -7757,12 +7757,12 @@
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>2600</t>
+          <t>2842</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>9799</t>
+          <t>10099</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -7772,12 +7772,12 @@
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>4,58%</t>
+          <t>5,01%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>17,27%</t>
+          <t>17,8%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -7792,12 +7792,12 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>3576</t>
+          <t>3504</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>12327</t>
+          <t>11944</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -7807,12 +7807,12 @@
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>3,24%</t>
+          <t>3,18%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>11,18%</t>
+          <t>10,83%</t>
         </is>
       </c>
     </row>
@@ -7835,7 +7835,7 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>49501</t>
+          <t>49419</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
@@ -7850,7 +7850,7 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>92,51%</t>
+          <t>92,36%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
@@ -7870,12 +7870,12 @@
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>46934</t>
+          <t>46634</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>54133</t>
+          <t>53891</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -7885,12 +7885,12 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>82,73%</t>
+          <t>82,2%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>95,42%</t>
+          <t>94,99%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -7905,12 +7905,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>97914</t>
+          <t>98297</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>106665</t>
+          <t>106737</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -7920,12 +7920,12 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>88,82%</t>
+          <t>89,17%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>96,76%</t>
+          <t>96,82%</t>
         </is>
       </c>
     </row>
@@ -8065,12 +8065,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>814</t>
+          <t>825</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>7054</t>
+          <t>7045</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -8080,12 +8080,12 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>2,5%</t>
+          <t>2,54%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>21,69%</t>
+          <t>21,66%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -8105,7 +8105,7 @@
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>3633</t>
+          <t>3671</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -8120,7 +8120,7 @@
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>11,31%</t>
+          <t>11,43%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -8135,12 +8135,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>1473</t>
+          <t>1505</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>8938</t>
+          <t>8361</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -8150,12 +8150,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>2,28%</t>
+          <t>2,33%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>13,83%</t>
+          <t>12,93%</t>
         </is>
       </c>
     </row>
@@ -8178,12 +8178,12 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>25463</t>
+          <t>25472</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>31703</t>
+          <t>31692</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -8193,12 +8193,12 @@
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>78,31%</t>
+          <t>78,34%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>97,5%</t>
+          <t>97,46%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -8213,7 +8213,7 @@
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>28491</t>
+          <t>28453</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
@@ -8228,7 +8228,7 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>88,69%</t>
+          <t>88,57%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
@@ -8248,12 +8248,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>55703</t>
+          <t>56280</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>63168</t>
+          <t>63136</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -8263,12 +8263,12 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>86,17%</t>
+          <t>87,07%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>97,72%</t>
+          <t>97,67%</t>
         </is>
       </c>
     </row>
@@ -8408,12 +8408,12 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>2851</t>
+          <t>2806</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>10676</t>
+          <t>10718</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -8423,12 +8423,12 @@
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>6,13%</t>
+          <t>6,03%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>22,94%</t>
+          <t>23,03%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -8443,12 +8443,12 @@
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>813</t>
+          <t>827</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>7202</t>
+          <t>7040</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -8458,12 +8458,12 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>1,59%</t>
+          <t>1,62%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>14,12%</t>
+          <t>13,8%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -8478,12 +8478,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>4739</t>
+          <t>4498</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>15064</t>
+          <t>14658</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -8493,12 +8493,12 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>4,86%</t>
+          <t>4,61%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>15,44%</t>
+          <t>15,03%</t>
         </is>
       </c>
     </row>
@@ -8521,12 +8521,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>35869</t>
+          <t>35827</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>43694</t>
+          <t>43739</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -8536,12 +8536,12 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>77,06%</t>
+          <t>76,97%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>93,87%</t>
+          <t>93,97%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -8556,12 +8556,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>43801</t>
+          <t>43963</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>50190</t>
+          <t>50176</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -8571,12 +8571,12 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>85,88%</t>
+          <t>86,2%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>98,41%</t>
+          <t>98,38%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -8591,12 +8591,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>82484</t>
+          <t>82890</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>92809</t>
+          <t>93050</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -8606,12 +8606,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>84,56%</t>
+          <t>84,97%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>95,14%</t>
+          <t>95,39%</t>
         </is>
       </c>
     </row>
@@ -8751,12 +8751,12 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>7775</t>
+          <t>7107</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>13444</t>
+          <t>13210</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -8766,12 +8766,12 @@
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>51,68%</t>
+          <t>47,24%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>89,36%</t>
+          <t>87,81%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -8786,12 +8786,12 @@
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>9486</t>
+          <t>9246</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>15168</t>
+          <t>15200</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
@@ -8801,12 +8801,12 @@
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>55,58%</t>
+          <t>54,17%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>88,87%</t>
+          <t>89,06%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -8821,12 +8821,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>19117</t>
+          <t>18162</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>27259</t>
+          <t>26691</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -8836,12 +8836,12 @@
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>59,53%</t>
+          <t>56,56%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>84,89%</t>
+          <t>83,12%</t>
         </is>
       </c>
     </row>
@@ -8864,12 +8864,12 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>1600</t>
+          <t>1834</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>7269</t>
+          <t>7937</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -8879,12 +8879,12 @@
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>10,64%</t>
+          <t>12,19%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>48,32%</t>
+          <t>52,76%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -8899,12 +8899,12 @@
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>1900</t>
+          <t>1868</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>7582</t>
+          <t>7822</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
@@ -8914,12 +8914,12 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>11,13%</t>
+          <t>10,94%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>44,42%</t>
+          <t>45,83%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -8934,12 +8934,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>4852</t>
+          <t>5420</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>12994</t>
+          <t>13949</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -8949,12 +8949,12 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>15,11%</t>
+          <t>16,88%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>40,47%</t>
+          <t>43,44%</t>
         </is>
       </c>
     </row>
@@ -9094,12 +9094,12 @@
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>5945</t>
+          <t>6603</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>15712</t>
+          <t>15671</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
@@ -9109,12 +9109,12 @@
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>14,96%</t>
+          <t>16,61%</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>39,54%</t>
+          <t>39,43%</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
@@ -9129,12 +9129,12 @@
       </c>
       <c r="L19" s="2" t="inlineStr">
         <is>
-          <t>4000</t>
+          <t>3968</t>
         </is>
       </c>
       <c r="M19" s="2" t="inlineStr">
         <is>
-          <t>13579</t>
+          <t>12986</t>
         </is>
       </c>
       <c r="N19" s="2" t="inlineStr">
@@ -9144,12 +9144,12 @@
       </c>
       <c r="O19" s="2" t="inlineStr">
         <is>
-          <t>9,86%</t>
+          <t>9,78%</t>
         </is>
       </c>
       <c r="P19" s="2" t="inlineStr">
         <is>
-          <t>33,47%</t>
+          <t>32,01%</t>
         </is>
       </c>
       <c r="Q19" s="2" t="inlineStr">
@@ -9164,12 +9164,12 @@
       </c>
       <c r="S19" s="2" t="inlineStr">
         <is>
-          <t>12762</t>
+          <t>12227</t>
         </is>
       </c>
       <c r="T19" s="2" t="inlineStr">
         <is>
-          <t>25369</t>
+          <t>25417</t>
         </is>
       </c>
       <c r="U19" s="2" t="inlineStr">
@@ -9179,12 +9179,12 @@
       </c>
       <c r="V19" s="2" t="inlineStr">
         <is>
-          <t>15,89%</t>
+          <t>15,22%</t>
         </is>
       </c>
       <c r="W19" s="2" t="inlineStr">
         <is>
-          <t>31,59%</t>
+          <t>31,65%</t>
         </is>
       </c>
     </row>
@@ -9207,12 +9207,12 @@
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>24031</t>
+          <t>24072</t>
         </is>
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>33798</t>
+          <t>33140</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
@@ -9222,12 +9222,12 @@
       </c>
       <c r="H20" s="2" t="inlineStr">
         <is>
-          <t>60,46%</t>
+          <t>60,57%</t>
         </is>
       </c>
       <c r="I20" s="2" t="inlineStr">
         <is>
-          <t>85,04%</t>
+          <t>83,39%</t>
         </is>
       </c>
       <c r="J20" s="2" t="inlineStr">
@@ -9242,12 +9242,12 @@
       </c>
       <c r="L20" s="2" t="inlineStr">
         <is>
-          <t>26991</t>
+          <t>27584</t>
         </is>
       </c>
       <c r="M20" s="2" t="inlineStr">
         <is>
-          <t>36570</t>
+          <t>36602</t>
         </is>
       </c>
       <c r="N20" s="2" t="inlineStr">
@@ -9257,12 +9257,12 @@
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>66,53%</t>
+          <t>67,99%</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
         <is>
-          <t>90,14%</t>
+          <t>90,22%</t>
         </is>
       </c>
       <c r="Q20" s="2" t="inlineStr">
@@ -9277,12 +9277,12 @@
       </c>
       <c r="S20" s="2" t="inlineStr">
         <is>
-          <t>54944</t>
+          <t>54896</t>
         </is>
       </c>
       <c r="T20" s="2" t="inlineStr">
         <is>
-          <t>67551</t>
+          <t>68086</t>
         </is>
       </c>
       <c r="U20" s="2" t="inlineStr">
@@ -9292,12 +9292,12 @@
       </c>
       <c r="V20" s="2" t="inlineStr">
         <is>
-          <t>68,41%</t>
+          <t>68,35%</t>
         </is>
       </c>
       <c r="W20" s="2" t="inlineStr">
         <is>
-          <t>84,11%</t>
+          <t>84,78%</t>
         </is>
       </c>
     </row>
@@ -9437,12 +9437,12 @@
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>5637</t>
+          <t>5383</t>
         </is>
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t>14888</t>
+          <t>14919</t>
         </is>
       </c>
       <c r="G22" s="2" t="inlineStr">
@@ -9452,12 +9452,12 @@
       </c>
       <c r="H22" s="2" t="inlineStr">
         <is>
-          <t>8,36%</t>
+          <t>7,98%</t>
         </is>
       </c>
       <c r="I22" s="2" t="inlineStr">
         <is>
-          <t>22,08%</t>
+          <t>22,12%</t>
         </is>
       </c>
       <c r="J22" s="2" t="inlineStr">
@@ -9472,12 +9472,12 @@
       </c>
       <c r="L22" s="2" t="inlineStr">
         <is>
-          <t>10289</t>
+          <t>9840</t>
         </is>
       </c>
       <c r="M22" s="2" t="inlineStr">
         <is>
-          <t>21730</t>
+          <t>21652</t>
         </is>
       </c>
       <c r="N22" s="2" t="inlineStr">
@@ -9487,12 +9487,12 @@
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>16,61%</t>
+          <t>15,89%</t>
         </is>
       </c>
       <c r="P22" s="2" t="inlineStr">
         <is>
-          <t>35,08%</t>
+          <t>34,95%</t>
         </is>
       </c>
       <c r="Q22" s="2" t="inlineStr">
@@ -9507,12 +9507,12 @@
       </c>
       <c r="S22" s="2" t="inlineStr">
         <is>
-          <t>17822</t>
+          <t>18380</t>
         </is>
       </c>
       <c r="T22" s="2" t="inlineStr">
         <is>
-          <t>33195</t>
+          <t>33008</t>
         </is>
       </c>
       <c r="U22" s="2" t="inlineStr">
@@ -9522,12 +9522,12 @@
       </c>
       <c r="V22" s="2" t="inlineStr">
         <is>
-          <t>13,77%</t>
+          <t>14,21%</t>
         </is>
       </c>
       <c r="W22" s="2" t="inlineStr">
         <is>
-          <t>25,66%</t>
+          <t>25,51%</t>
         </is>
       </c>
     </row>
@@ -9550,12 +9550,12 @@
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t>52555</t>
+          <t>52524</t>
         </is>
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
-          <t>61806</t>
+          <t>62060</t>
         </is>
       </c>
       <c r="G23" s="2" t="inlineStr">
@@ -9565,12 +9565,12 @@
       </c>
       <c r="H23" s="2" t="inlineStr">
         <is>
-          <t>77,92%</t>
+          <t>77,88%</t>
         </is>
       </c>
       <c r="I23" s="2" t="inlineStr">
         <is>
-          <t>91,64%</t>
+          <t>92,02%</t>
         </is>
       </c>
       <c r="J23" s="2" t="inlineStr">
@@ -9585,12 +9585,12 @@
       </c>
       <c r="L23" s="2" t="inlineStr">
         <is>
-          <t>40213</t>
+          <t>40291</t>
         </is>
       </c>
       <c r="M23" s="2" t="inlineStr">
         <is>
-          <t>51654</t>
+          <t>52103</t>
         </is>
       </c>
       <c r="N23" s="2" t="inlineStr">
@@ -9600,12 +9600,12 @@
       </c>
       <c r="O23" s="2" t="inlineStr">
         <is>
-          <t>64,92%</t>
+          <t>65,05%</t>
         </is>
       </c>
       <c r="P23" s="2" t="inlineStr">
         <is>
-          <t>83,39%</t>
+          <t>84,11%</t>
         </is>
       </c>
       <c r="Q23" s="2" t="inlineStr">
@@ -9620,12 +9620,12 @@
       </c>
       <c r="S23" s="2" t="inlineStr">
         <is>
-          <t>96191</t>
+          <t>96378</t>
         </is>
       </c>
       <c r="T23" s="2" t="inlineStr">
         <is>
-          <t>111564</t>
+          <t>111006</t>
         </is>
       </c>
       <c r="U23" s="2" t="inlineStr">
@@ -9635,12 +9635,12 @@
       </c>
       <c r="V23" s="2" t="inlineStr">
         <is>
-          <t>74,34%</t>
+          <t>74,49%</t>
         </is>
       </c>
       <c r="W23" s="2" t="inlineStr">
         <is>
-          <t>86,23%</t>
+          <t>85,79%</t>
         </is>
       </c>
     </row>
@@ -9780,12 +9780,12 @@
       </c>
       <c r="E25" s="2" t="inlineStr">
         <is>
-          <t>19147</t>
+          <t>19518</t>
         </is>
       </c>
       <c r="F25" s="2" t="inlineStr">
         <is>
-          <t>31939</t>
+          <t>32760</t>
         </is>
       </c>
       <c r="G25" s="2" t="inlineStr">
@@ -9795,12 +9795,12 @@
       </c>
       <c r="H25" s="2" t="inlineStr">
         <is>
-          <t>24,16%</t>
+          <t>24,63%</t>
         </is>
       </c>
       <c r="I25" s="2" t="inlineStr">
         <is>
-          <t>40,3%</t>
+          <t>41,34%</t>
         </is>
       </c>
       <c r="J25" s="2" t="inlineStr">
@@ -9815,12 +9815,12 @@
       </c>
       <c r="L25" s="2" t="inlineStr">
         <is>
-          <t>19216</t>
+          <t>18696</t>
         </is>
       </c>
       <c r="M25" s="2" t="inlineStr">
         <is>
-          <t>33540</t>
+          <t>33018</t>
         </is>
       </c>
       <c r="N25" s="2" t="inlineStr">
@@ -9830,12 +9830,12 @@
       </c>
       <c r="O25" s="2" t="inlineStr">
         <is>
-          <t>24,43%</t>
+          <t>23,77%</t>
         </is>
       </c>
       <c r="P25" s="2" t="inlineStr">
         <is>
-          <t>42,64%</t>
+          <t>41,98%</t>
         </is>
       </c>
       <c r="Q25" s="2" t="inlineStr">
@@ -9850,12 +9850,12 @@
       </c>
       <c r="S25" s="2" t="inlineStr">
         <is>
-          <t>42086</t>
+          <t>42474</t>
         </is>
       </c>
       <c r="T25" s="2" t="inlineStr">
         <is>
-          <t>61030</t>
+          <t>61511</t>
         </is>
       </c>
       <c r="U25" s="2" t="inlineStr">
@@ -9865,12 +9865,12 @@
       </c>
       <c r="V25" s="2" t="inlineStr">
         <is>
-          <t>26,65%</t>
+          <t>26,9%</t>
         </is>
       </c>
       <c r="W25" s="2" t="inlineStr">
         <is>
-          <t>38,65%</t>
+          <t>38,95%</t>
         </is>
       </c>
     </row>
@@ -9893,12 +9893,12 @@
       </c>
       <c r="E26" s="2" t="inlineStr">
         <is>
-          <t>47313</t>
+          <t>46492</t>
         </is>
       </c>
       <c r="F26" s="2" t="inlineStr">
         <is>
-          <t>60105</t>
+          <t>59734</t>
         </is>
       </c>
       <c r="G26" s="2" t="inlineStr">
@@ -9908,12 +9908,12 @@
       </c>
       <c r="H26" s="2" t="inlineStr">
         <is>
-          <t>59,7%</t>
+          <t>58,66%</t>
         </is>
       </c>
       <c r="I26" s="2" t="inlineStr">
         <is>
-          <t>75,84%</t>
+          <t>75,37%</t>
         </is>
       </c>
       <c r="J26" s="2" t="inlineStr">
@@ -9928,12 +9928,12 @@
       </c>
       <c r="L26" s="2" t="inlineStr">
         <is>
-          <t>45118</t>
+          <t>45640</t>
         </is>
       </c>
       <c r="M26" s="2" t="inlineStr">
         <is>
-          <t>59442</t>
+          <t>59962</t>
         </is>
       </c>
       <c r="N26" s="2" t="inlineStr">
@@ -9943,12 +9943,12 @@
       </c>
       <c r="O26" s="2" t="inlineStr">
         <is>
-          <t>57,36%</t>
+          <t>58,02%</t>
         </is>
       </c>
       <c r="P26" s="2" t="inlineStr">
         <is>
-          <t>75,57%</t>
+          <t>76,23%</t>
         </is>
       </c>
       <c r="Q26" s="2" t="inlineStr">
@@ -9963,12 +9963,12 @@
       </c>
       <c r="S26" s="2" t="inlineStr">
         <is>
-          <t>96880</t>
+          <t>96399</t>
         </is>
       </c>
       <c r="T26" s="2" t="inlineStr">
         <is>
-          <t>115824</t>
+          <t>115436</t>
         </is>
       </c>
       <c r="U26" s="2" t="inlineStr">
@@ -9978,12 +9978,12 @@
       </c>
       <c r="V26" s="2" t="inlineStr">
         <is>
-          <t>61,35%</t>
+          <t>61,05%</t>
         </is>
       </c>
       <c r="W26" s="2" t="inlineStr">
         <is>
-          <t>73,35%</t>
+          <t>73,1%</t>
         </is>
       </c>
     </row>
@@ -10123,12 +10123,12 @@
       </c>
       <c r="E28" s="2" t="inlineStr">
         <is>
-          <t>57080</t>
+          <t>56846</t>
         </is>
       </c>
       <c r="F28" s="2" t="inlineStr">
         <is>
-          <t>82128</t>
+          <t>81368</t>
         </is>
       </c>
       <c r="G28" s="2" t="inlineStr">
@@ -10138,12 +10138,12 @@
       </c>
       <c r="H28" s="2" t="inlineStr">
         <is>
-          <t>15,74%</t>
+          <t>15,68%</t>
         </is>
       </c>
       <c r="I28" s="2" t="inlineStr">
         <is>
-          <t>22,65%</t>
+          <t>22,44%</t>
         </is>
       </c>
       <c r="J28" s="2" t="inlineStr">
@@ -10158,12 +10158,12 @@
       </c>
       <c r="L28" s="2" t="inlineStr">
         <is>
-          <t>59392</t>
+          <t>60081</t>
         </is>
       </c>
       <c r="M28" s="2" t="inlineStr">
         <is>
-          <t>85650</t>
+          <t>86057</t>
         </is>
       </c>
       <c r="N28" s="2" t="inlineStr">
@@ -10173,12 +10173,12 @@
       </c>
       <c r="O28" s="2" t="inlineStr">
         <is>
-          <t>16,14%</t>
+          <t>16,33%</t>
         </is>
       </c>
       <c r="P28" s="2" t="inlineStr">
         <is>
-          <t>23,27%</t>
+          <t>23,38%</t>
         </is>
       </c>
       <c r="Q28" s="2" t="inlineStr">
@@ -10193,12 +10193,12 @@
       </c>
       <c r="S28" s="2" t="inlineStr">
         <is>
-          <t>123958</t>
+          <t>124700</t>
         </is>
       </c>
       <c r="T28" s="2" t="inlineStr">
         <is>
-          <t>159082</t>
+          <t>158533</t>
         </is>
       </c>
       <c r="U28" s="2" t="inlineStr">
@@ -10208,12 +10208,12 @@
       </c>
       <c r="V28" s="2" t="inlineStr">
         <is>
-          <t>16,97%</t>
+          <t>17,07%</t>
         </is>
       </c>
       <c r="W28" s="2" t="inlineStr">
         <is>
-          <t>21,77%</t>
+          <t>21,7%</t>
         </is>
       </c>
     </row>
@@ -10236,12 +10236,12 @@
       </c>
       <c r="E29" s="2" t="inlineStr">
         <is>
-          <t>280490</t>
+          <t>281250</t>
         </is>
       </c>
       <c r="F29" s="2" t="inlineStr">
         <is>
-          <t>305538</t>
+          <t>305772</t>
         </is>
       </c>
       <c r="G29" s="2" t="inlineStr">
@@ -10251,12 +10251,12 @@
       </c>
       <c r="H29" s="2" t="inlineStr">
         <is>
-          <t>77,35%</t>
+          <t>77,56%</t>
         </is>
       </c>
       <c r="I29" s="2" t="inlineStr">
         <is>
-          <t>84,26%</t>
+          <t>84,32%</t>
         </is>
       </c>
       <c r="J29" s="2" t="inlineStr">
@@ -10271,12 +10271,12 @@
       </c>
       <c r="L29" s="2" t="inlineStr">
         <is>
-          <t>282358</t>
+          <t>281951</t>
         </is>
       </c>
       <c r="M29" s="2" t="inlineStr">
         <is>
-          <t>308616</t>
+          <t>307927</t>
         </is>
       </c>
       <c r="N29" s="2" t="inlineStr">
@@ -10286,12 +10286,12 @@
       </c>
       <c r="O29" s="2" t="inlineStr">
         <is>
-          <t>76,73%</t>
+          <t>76,62%</t>
         </is>
       </c>
       <c r="P29" s="2" t="inlineStr">
         <is>
-          <t>83,86%</t>
+          <t>83,67%</t>
         </is>
       </c>
       <c r="Q29" s="2" t="inlineStr">
@@ -10306,12 +10306,12 @@
       </c>
       <c r="S29" s="2" t="inlineStr">
         <is>
-          <t>571544</t>
+          <t>572093</t>
         </is>
       </c>
       <c r="T29" s="2" t="inlineStr">
         <is>
-          <t>606668</t>
+          <t>605926</t>
         </is>
       </c>
       <c r="U29" s="2" t="inlineStr">
@@ -10321,12 +10321,12 @@
       </c>
       <c r="V29" s="2" t="inlineStr">
         <is>
-          <t>78,23%</t>
+          <t>78,3%</t>
         </is>
       </c>
       <c r="W29" s="2" t="inlineStr">
         <is>
-          <t>83,03%</t>
+          <t>82,93%</t>
         </is>
       </c>
     </row>
@@ -10702,12 +10702,12 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>1935</t>
+          <t>2110</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>13511</t>
+          <t>13269</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -10717,12 +10717,12 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>5,56%</t>
+          <t>6,06%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>38,8%</t>
+          <t>38,11%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -10737,12 +10737,12 @@
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>1758</t>
+          <t>1886</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>10836</t>
+          <t>10300</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -10752,12 +10752,12 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>4,41%</t>
+          <t>4,73%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>27,18%</t>
+          <t>25,84%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -10772,12 +10772,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>5600</t>
+          <t>5418</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>21314</t>
+          <t>19572</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -10787,12 +10787,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>7,5%</t>
+          <t>7,26%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>28,54%</t>
+          <t>26,21%</t>
         </is>
       </c>
     </row>
@@ -10815,12 +10815,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>21307</t>
+          <t>21549</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>32883</t>
+          <t>32708</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -10830,12 +10830,12 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>61,2%</t>
+          <t>61,89%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>94,44%</t>
+          <t>93,94%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -10850,12 +10850,12 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>29029</t>
+          <t>29565</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>38107</t>
+          <t>37979</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -10865,12 +10865,12 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>72,82%</t>
+          <t>74,16%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>95,59%</t>
+          <t>95,27%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -10885,12 +10885,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>53368</t>
+          <t>55110</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>69082</t>
+          <t>69264</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -10900,12 +10900,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>71,46%</t>
+          <t>73,79%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>92,5%</t>
+          <t>92,74%</t>
         </is>
       </c>
     </row>
@@ -11045,12 +11045,12 @@
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>1614</t>
+          <t>1582</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>10048</t>
+          <t>10128</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -11060,12 +11060,12 @@
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>2,34%</t>
+          <t>2,3%</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>14,6%</t>
+          <t>14,71%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -11080,12 +11080,12 @@
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>2680</t>
+          <t>3185</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>12373</t>
+          <t>13092</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -11095,12 +11095,12 @@
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>3,63%</t>
+          <t>4,31%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>16,76%</t>
+          <t>17,73%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -11115,12 +11115,12 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>6028</t>
+          <t>5867</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>18968</t>
+          <t>18530</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -11130,12 +11130,12 @@
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>4,22%</t>
+          <t>4,11%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>13,29%</t>
+          <t>12,99%</t>
         </is>
       </c>
     </row>
@@ -11158,12 +11158,12 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>58796</t>
+          <t>58716</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>67230</t>
+          <t>67262</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -11173,12 +11173,12 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>85,4%</t>
+          <t>85,29%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>97,66%</t>
+          <t>97,7%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -11193,12 +11193,12 @@
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>61456</t>
+          <t>60737</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>71149</t>
+          <t>70644</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -11208,12 +11208,12 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>83,24%</t>
+          <t>82,27%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>96,37%</t>
+          <t>95,69%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -11228,12 +11228,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>123705</t>
+          <t>124143</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>136645</t>
+          <t>136806</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -11243,12 +11243,12 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>86,71%</t>
+          <t>87,01%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>95,78%</t>
+          <t>95,89%</t>
         </is>
       </c>
     </row>
@@ -11388,12 +11388,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>594</t>
+          <t>587</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>5092</t>
+          <t>5098</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -11403,12 +11403,12 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>1,87%</t>
+          <t>1,84%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>16,0%</t>
+          <t>16,02%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -11423,12 +11423,12 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>638</t>
+          <t>645</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>6449</t>
+          <t>7125</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -11438,12 +11438,12 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>1,59%</t>
+          <t>1,61%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>16,1%</t>
+          <t>17,79%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -11458,12 +11458,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>1882</t>
+          <t>1908</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>9245</t>
+          <t>9416</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -11473,12 +11473,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>2,62%</t>
+          <t>2,65%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>12,86%</t>
+          <t>13,1%</t>
         </is>
       </c>
     </row>
@@ -11501,12 +11501,12 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>26731</t>
+          <t>26725</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>31229</t>
+          <t>31236</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -11516,12 +11516,12 @@
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>84,0%</t>
+          <t>83,98%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>98,13%</t>
+          <t>98,16%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -11536,12 +11536,12 @@
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>33603</t>
+          <t>32927</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>39414</t>
+          <t>39407</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
@@ -11551,12 +11551,12 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>83,9%</t>
+          <t>82,21%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>98,41%</t>
+          <t>98,39%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -11571,12 +11571,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>62629</t>
+          <t>62458</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>69992</t>
+          <t>69966</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -11586,12 +11586,12 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>87,14%</t>
+          <t>86,9%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>97,38%</t>
+          <t>97,35%</t>
         </is>
       </c>
     </row>
@@ -11731,12 +11731,12 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>1941</t>
+          <t>1993</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>9474</t>
+          <t>9954</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -11746,12 +11746,12 @@
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>4,53%</t>
+          <t>4,65%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>22,11%</t>
+          <t>23,23%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -11766,12 +11766,12 @@
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>1015</t>
+          <t>1441</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>14866</t>
+          <t>15843</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -11781,12 +11781,12 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>1,73%</t>
+          <t>2,46%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>25,34%</t>
+          <t>27,01%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -11801,12 +11801,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>5057</t>
+          <t>4823</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>19886</t>
+          <t>19833</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -11816,12 +11816,12 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>4,98%</t>
+          <t>4,75%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>19,59%</t>
+          <t>19,54%</t>
         </is>
       </c>
     </row>
@@ -11844,12 +11844,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>33369</t>
+          <t>32889</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>40902</t>
+          <t>40850</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -11859,12 +11859,12 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>77,89%</t>
+          <t>76,77%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>95,47%</t>
+          <t>95,35%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -11879,12 +11879,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>43795</t>
+          <t>42818</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>57646</t>
+          <t>57220</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -11894,12 +11894,12 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>74,66%</t>
+          <t>72,99%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>98,27%</t>
+          <t>97,54%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -11914,12 +11914,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>81618</t>
+          <t>81671</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>96447</t>
+          <t>96681</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -11929,12 +11929,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>80,41%</t>
+          <t>80,46%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>95,02%</t>
+          <t>95,25%</t>
         </is>
       </c>
     </row>
@@ -12074,12 +12074,12 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>15007</t>
+          <t>14632</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>21136</t>
+          <t>20910</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -12089,12 +12089,12 @@
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>59,34%</t>
+          <t>57,85%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>83,57%</t>
+          <t>82,67%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -12109,12 +12109,12 @@
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>21146</t>
+          <t>21363</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>29191</t>
+          <t>29328</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
@@ -12124,12 +12124,12 @@
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>61,07%</t>
+          <t>61,7%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>84,3%</t>
+          <t>84,7%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -12144,12 +12144,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>38139</t>
+          <t>37862</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>48457</t>
+          <t>48350</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -12159,12 +12159,12 @@
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>63,65%</t>
+          <t>63,19%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>80,87%</t>
+          <t>80,69%</t>
         </is>
       </c>
     </row>
@@ -12187,12 +12187,12 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>4156</t>
+          <t>4382</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>10285</t>
+          <t>10660</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -12202,12 +12202,12 @@
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>16,43%</t>
+          <t>17,33%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>40,66%</t>
+          <t>42,15%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -12222,12 +12222,12 @@
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>5436</t>
+          <t>5299</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>13481</t>
+          <t>13264</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
@@ -12237,12 +12237,12 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>15,7%</t>
+          <t>15,3%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>38,93%</t>
+          <t>38,3%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -12257,12 +12257,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>11462</t>
+          <t>11569</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>21780</t>
+          <t>22057</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -12272,12 +12272,12 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>19,13%</t>
+          <t>19,31%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>36,35%</t>
+          <t>36,81%</t>
         </is>
       </c>
     </row>
@@ -12422,7 +12422,7 @@
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>3772</t>
+          <t>3424</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
@@ -12437,7 +12437,7 @@
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>13,99%</t>
+          <t>12,7%</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
@@ -12492,7 +12492,7 @@
       </c>
       <c r="T19" s="2" t="inlineStr">
         <is>
-          <t>3680</t>
+          <t>3369</t>
         </is>
       </c>
       <c r="U19" s="2" t="inlineStr">
@@ -12507,7 +12507,7 @@
       </c>
       <c r="W19" s="2" t="inlineStr">
         <is>
-          <t>6,83%</t>
+          <t>6,25%</t>
         </is>
       </c>
     </row>
@@ -12530,7 +12530,7 @@
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>23190</t>
+          <t>23538</t>
         </is>
       </c>
       <c r="F20" s="2" t="inlineStr">
@@ -12545,7 +12545,7 @@
       </c>
       <c r="H20" s="2" t="inlineStr">
         <is>
-          <t>86,01%</t>
+          <t>87,3%</t>
         </is>
       </c>
       <c r="I20" s="2" t="inlineStr">
@@ -12600,7 +12600,7 @@
       </c>
       <c r="S20" s="2" t="inlineStr">
         <is>
-          <t>50227</t>
+          <t>50538</t>
         </is>
       </c>
       <c r="T20" s="2" t="inlineStr">
@@ -12615,7 +12615,7 @@
       </c>
       <c r="V20" s="2" t="inlineStr">
         <is>
-          <t>93,17%</t>
+          <t>93,75%</t>
         </is>
       </c>
       <c r="W20" s="2" t="inlineStr">
@@ -12760,12 +12760,12 @@
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>7412</t>
+          <t>7186</t>
         </is>
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t>18943</t>
+          <t>18370</t>
         </is>
       </c>
       <c r="G22" s="2" t="inlineStr">
@@ -12775,12 +12775,12 @@
       </c>
       <c r="H22" s="2" t="inlineStr">
         <is>
-          <t>9,53%</t>
+          <t>9,24%</t>
         </is>
       </c>
       <c r="I22" s="2" t="inlineStr">
         <is>
-          <t>24,36%</t>
+          <t>23,62%</t>
         </is>
       </c>
       <c r="J22" s="2" t="inlineStr">
@@ -12795,12 +12795,12 @@
       </c>
       <c r="L22" s="2" t="inlineStr">
         <is>
-          <t>15018</t>
+          <t>14396</t>
         </is>
       </c>
       <c r="M22" s="2" t="inlineStr">
         <is>
-          <t>35639</t>
+          <t>35250</t>
         </is>
       </c>
       <c r="N22" s="2" t="inlineStr">
@@ -12810,12 +12810,12 @@
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>13,82%</t>
+          <t>13,25%</t>
         </is>
       </c>
       <c r="P22" s="2" t="inlineStr">
         <is>
-          <t>32,79%</t>
+          <t>32,43%</t>
         </is>
       </c>
       <c r="Q22" s="2" t="inlineStr">
@@ -12830,12 +12830,12 @@
       </c>
       <c r="S22" s="2" t="inlineStr">
         <is>
-          <t>25755</t>
+          <t>24892</t>
         </is>
       </c>
       <c r="T22" s="2" t="inlineStr">
         <is>
-          <t>48642</t>
+          <t>48098</t>
         </is>
       </c>
       <c r="U22" s="2" t="inlineStr">
@@ -12845,12 +12845,12 @@
       </c>
       <c r="V22" s="2" t="inlineStr">
         <is>
-          <t>13,81%</t>
+          <t>13,35%</t>
         </is>
       </c>
       <c r="W22" s="2" t="inlineStr">
         <is>
-          <t>26,09%</t>
+          <t>25,8%</t>
         </is>
       </c>
     </row>
@@ -12873,12 +12873,12 @@
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t>58813</t>
+          <t>59386</t>
         </is>
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
-          <t>70344</t>
+          <t>70570</t>
         </is>
       </c>
       <c r="G23" s="2" t="inlineStr">
@@ -12888,12 +12888,12 @@
       </c>
       <c r="H23" s="2" t="inlineStr">
         <is>
-          <t>75,64%</t>
+          <t>76,38%</t>
         </is>
       </c>
       <c r="I23" s="2" t="inlineStr">
         <is>
-          <t>90,47%</t>
+          <t>90,76%</t>
         </is>
       </c>
       <c r="J23" s="2" t="inlineStr">
@@ -12908,12 +12908,12 @@
       </c>
       <c r="L23" s="2" t="inlineStr">
         <is>
-          <t>73049</t>
+          <t>73438</t>
         </is>
       </c>
       <c r="M23" s="2" t="inlineStr">
         <is>
-          <t>93670</t>
+          <t>94292</t>
         </is>
       </c>
       <c r="N23" s="2" t="inlineStr">
@@ -12923,12 +12923,12 @@
       </c>
       <c r="O23" s="2" t="inlineStr">
         <is>
-          <t>67,21%</t>
+          <t>67,57%</t>
         </is>
       </c>
       <c r="P23" s="2" t="inlineStr">
         <is>
-          <t>86,18%</t>
+          <t>86,75%</t>
         </is>
       </c>
       <c r="Q23" s="2" t="inlineStr">
@@ -12943,12 +12943,12 @@
       </c>
       <c r="S23" s="2" t="inlineStr">
         <is>
-          <t>137802</t>
+          <t>138346</t>
         </is>
       </c>
       <c r="T23" s="2" t="inlineStr">
         <is>
-          <t>160689</t>
+          <t>161552</t>
         </is>
       </c>
       <c r="U23" s="2" t="inlineStr">
@@ -12958,12 +12958,12 @@
       </c>
       <c r="V23" s="2" t="inlineStr">
         <is>
-          <t>73,91%</t>
+          <t>74,2%</t>
         </is>
       </c>
       <c r="W23" s="2" t="inlineStr">
         <is>
-          <t>86,19%</t>
+          <t>86,65%</t>
         </is>
       </c>
     </row>
@@ -13103,12 +13103,12 @@
       </c>
       <c r="E25" s="2" t="inlineStr">
         <is>
-          <t>61208</t>
+          <t>60887</t>
         </is>
       </c>
       <c r="F25" s="2" t="inlineStr">
         <is>
-          <t>73269</t>
+          <t>72768</t>
         </is>
       </c>
       <c r="G25" s="2" t="inlineStr">
@@ -13118,12 +13118,12 @@
       </c>
       <c r="H25" s="2" t="inlineStr">
         <is>
-          <t>73,48%</t>
+          <t>73,1%</t>
         </is>
       </c>
       <c r="I25" s="2" t="inlineStr">
         <is>
-          <t>87,96%</t>
+          <t>87,36%</t>
         </is>
       </c>
       <c r="J25" s="2" t="inlineStr">
@@ -13138,12 +13138,12 @@
       </c>
       <c r="L25" s="2" t="inlineStr">
         <is>
-          <t>76629</t>
+          <t>76656</t>
         </is>
       </c>
       <c r="M25" s="2" t="inlineStr">
         <is>
-          <t>90100</t>
+          <t>90207</t>
         </is>
       </c>
       <c r="N25" s="2" t="inlineStr">
@@ -13153,12 +13153,12 @@
       </c>
       <c r="O25" s="2" t="inlineStr">
         <is>
-          <t>75,29%</t>
+          <t>75,32%</t>
         </is>
       </c>
       <c r="P25" s="2" t="inlineStr">
         <is>
-          <t>88,53%</t>
+          <t>88,63%</t>
         </is>
       </c>
       <c r="Q25" s="2" t="inlineStr">
@@ -13173,12 +13173,12 @@
       </c>
       <c r="S25" s="2" t="inlineStr">
         <is>
-          <t>142539</t>
+          <t>141267</t>
         </is>
       </c>
       <c r="T25" s="2" t="inlineStr">
         <is>
-          <t>161194</t>
+          <t>160955</t>
         </is>
       </c>
       <c r="U25" s="2" t="inlineStr">
@@ -13188,12 +13188,12 @@
       </c>
       <c r="V25" s="2" t="inlineStr">
         <is>
-          <t>77,02%</t>
+          <t>76,33%</t>
         </is>
       </c>
       <c r="W25" s="2" t="inlineStr">
         <is>
-          <t>87,1%</t>
+          <t>86,97%</t>
         </is>
       </c>
     </row>
@@ -13216,12 +13216,12 @@
       </c>
       <c r="E26" s="2" t="inlineStr">
         <is>
-          <t>10026</t>
+          <t>10527</t>
         </is>
       </c>
       <c r="F26" s="2" t="inlineStr">
         <is>
-          <t>22087</t>
+          <t>22408</t>
         </is>
       </c>
       <c r="G26" s="2" t="inlineStr">
@@ -13231,12 +13231,12 @@
       </c>
       <c r="H26" s="2" t="inlineStr">
         <is>
-          <t>12,04%</t>
+          <t>12,64%</t>
         </is>
       </c>
       <c r="I26" s="2" t="inlineStr">
         <is>
-          <t>26,52%</t>
+          <t>26,9%</t>
         </is>
       </c>
       <c r="J26" s="2" t="inlineStr">
@@ -13251,12 +13251,12 @@
       </c>
       <c r="L26" s="2" t="inlineStr">
         <is>
-          <t>11677</t>
+          <t>11570</t>
         </is>
       </c>
       <c r="M26" s="2" t="inlineStr">
         <is>
-          <t>25148</t>
+          <t>25121</t>
         </is>
       </c>
       <c r="N26" s="2" t="inlineStr">
@@ -13266,12 +13266,12 @@
       </c>
       <c r="O26" s="2" t="inlineStr">
         <is>
-          <t>11,47%</t>
+          <t>11,37%</t>
         </is>
       </c>
       <c r="P26" s="2" t="inlineStr">
         <is>
-          <t>24,71%</t>
+          <t>24,68%</t>
         </is>
       </c>
       <c r="Q26" s="2" t="inlineStr">
@@ -13286,12 +13286,12 @@
       </c>
       <c r="S26" s="2" t="inlineStr">
         <is>
-          <t>23878</t>
+          <t>24117</t>
         </is>
       </c>
       <c r="T26" s="2" t="inlineStr">
         <is>
-          <t>42533</t>
+          <t>43805</t>
         </is>
       </c>
       <c r="U26" s="2" t="inlineStr">
@@ -13301,12 +13301,12 @@
       </c>
       <c r="V26" s="2" t="inlineStr">
         <is>
-          <t>12,9%</t>
+          <t>13,03%</t>
         </is>
       </c>
       <c r="W26" s="2" t="inlineStr">
         <is>
-          <t>22,98%</t>
+          <t>23,67%</t>
         </is>
       </c>
     </row>
@@ -13446,12 +13446,12 @@
       </c>
       <c r="E28" s="2" t="inlineStr">
         <is>
-          <t>100387</t>
+          <t>100101</t>
         </is>
       </c>
       <c r="F28" s="2" t="inlineStr">
         <is>
-          <t>133507</t>
+          <t>131230</t>
         </is>
       </c>
       <c r="G28" s="2" t="inlineStr">
@@ -13461,12 +13461,12 @@
       </c>
       <c r="H28" s="2" t="inlineStr">
         <is>
-          <t>25,63%</t>
+          <t>25,56%</t>
         </is>
       </c>
       <c r="I28" s="2" t="inlineStr">
         <is>
-          <t>34,09%</t>
+          <t>33,51%</t>
         </is>
       </c>
       <c r="J28" s="2" t="inlineStr">
@@ -13481,12 +13481,12 @@
       </c>
       <c r="L28" s="2" t="inlineStr">
         <is>
-          <t>132619</t>
+          <t>131763</t>
         </is>
       </c>
       <c r="M28" s="2" t="inlineStr">
         <is>
-          <t>173719</t>
+          <t>173549</t>
         </is>
       </c>
       <c r="N28" s="2" t="inlineStr">
@@ -13496,12 +13496,12 @@
       </c>
       <c r="O28" s="2" t="inlineStr">
         <is>
-          <t>27,38%</t>
+          <t>27,2%</t>
         </is>
       </c>
       <c r="P28" s="2" t="inlineStr">
         <is>
-          <t>35,86%</t>
+          <t>35,82%</t>
         </is>
       </c>
       <c r="Q28" s="2" t="inlineStr">
@@ -13516,12 +13516,12 @@
       </c>
       <c r="S28" s="2" t="inlineStr">
         <is>
-          <t>242682</t>
+          <t>243120</t>
         </is>
       </c>
       <c r="T28" s="2" t="inlineStr">
         <is>
-          <t>295243</t>
+          <t>295973</t>
         </is>
       </c>
       <c r="U28" s="2" t="inlineStr">
@@ -13531,12 +13531,12 @@
       </c>
       <c r="V28" s="2" t="inlineStr">
         <is>
-          <t>27,7%</t>
+          <t>27,75%</t>
         </is>
       </c>
       <c r="W28" s="2" t="inlineStr">
         <is>
-          <t>33,7%</t>
+          <t>33,78%</t>
         </is>
       </c>
     </row>
@@ -13559,12 +13559,12 @@
       </c>
       <c r="E29" s="2" t="inlineStr">
         <is>
-          <t>258126</t>
+          <t>260403</t>
         </is>
       </c>
       <c r="F29" s="2" t="inlineStr">
         <is>
-          <t>291246</t>
+          <t>291532</t>
         </is>
       </c>
       <c r="G29" s="2" t="inlineStr">
@@ -13574,12 +13574,12 @@
       </c>
       <c r="H29" s="2" t="inlineStr">
         <is>
-          <t>65,91%</t>
+          <t>66,49%</t>
         </is>
       </c>
       <c r="I29" s="2" t="inlineStr">
         <is>
-          <t>74,37%</t>
+          <t>74,44%</t>
         </is>
       </c>
       <c r="J29" s="2" t="inlineStr">
@@ -13594,12 +13594,12 @@
       </c>
       <c r="L29" s="2" t="inlineStr">
         <is>
-          <t>310725</t>
+          <t>310895</t>
         </is>
       </c>
       <c r="M29" s="2" t="inlineStr">
         <is>
-          <t>351825</t>
+          <t>352681</t>
         </is>
       </c>
       <c r="N29" s="2" t="inlineStr">
@@ -13609,12 +13609,12 @@
       </c>
       <c r="O29" s="2" t="inlineStr">
         <is>
-          <t>64,14%</t>
+          <t>64,18%</t>
         </is>
       </c>
       <c r="P29" s="2" t="inlineStr">
         <is>
-          <t>72,62%</t>
+          <t>72,8%</t>
         </is>
       </c>
       <c r="Q29" s="2" t="inlineStr">
@@ -13629,12 +13629,12 @@
       </c>
       <c r="S29" s="2" t="inlineStr">
         <is>
-          <t>580833</t>
+          <t>580103</t>
         </is>
       </c>
       <c r="T29" s="2" t="inlineStr">
         <is>
-          <t>633394</t>
+          <t>632956</t>
         </is>
       </c>
       <c r="U29" s="2" t="inlineStr">
@@ -13644,12 +13644,12 @@
       </c>
       <c r="V29" s="2" t="inlineStr">
         <is>
-          <t>66,3%</t>
+          <t>66,22%</t>
         </is>
       </c>
       <c r="W29" s="2" t="inlineStr">
         <is>
-          <t>72,3%</t>
+          <t>72,25%</t>
         </is>
       </c>
     </row>
